--- a/output/pdf_financials_xlsx/ICGH.xlsx
+++ b/output/pdf_financials_xlsx/ICGH.xlsx
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>4.769602</v>
+        <v>0.101329</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>9.043186</v>
+        <v>4.81072</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>4.769602</v>
+        <v>0.101329</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>9.043186</v>
+        <v>4.81072</v>
       </c>
     </row>
     <row r="37">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.842105</v>
+        <v>5.510378</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.113746</v>
+        <v>9.346212</v>
       </c>
     </row>
     <row r="49">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">

--- a/output/pdf_financials_xlsx/ICGH.xlsx
+++ b/output/pdf_financials_xlsx/ICGH.xlsx
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.204572</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.73526</v>
       </c>
     </row>
     <row r="101">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">

--- a/output/pdf_financials_xlsx/ICGH.xlsx
+++ b/output/pdf_financials_xlsx/ICGH.xlsx
@@ -3214,7 +3214,11 @@
           <t>Deferred Income tax expense (recovery) 13</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>-0.235468</v>
       </c>
